--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/194.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/194.xlsx
@@ -426,13 +426,13 @@
         <v>-10.74771929925075</v>
       </c>
       <c r="E2">
-        <v>-9.734255835479541</v>
+        <v>-10.52439756575989</v>
       </c>
       <c r="F2">
-        <v>1.708448242398579</v>
+        <v>0.6871543064736502</v>
       </c>
       <c r="G2">
-        <v>-4.240631217015604</v>
+        <v>-5.114734419022611</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.74428061624792</v>
       </c>
       <c r="E3">
-        <v>-8.655179349613794</v>
+        <v>-13.82279312177873</v>
       </c>
       <c r="F3">
-        <v>1.46848670579711</v>
+        <v>0.4638881976327432</v>
       </c>
       <c r="G3">
-        <v>-5.158244919045252</v>
+        <v>-4.414858607656368</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.68350800404333</v>
       </c>
       <c r="E4">
-        <v>-9.892290521399222</v>
+        <v>-14.01405322149269</v>
       </c>
       <c r="F4">
-        <v>1.650424425068709</v>
+        <v>0.8344706307278276</v>
       </c>
       <c r="G4">
-        <v>-4.404698543396345</v>
+        <v>-5.611180517546179</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.55294945291596</v>
       </c>
       <c r="E5">
-        <v>-11.30633370113834</v>
+        <v>-14.951180161114</v>
       </c>
       <c r="F5">
-        <v>1.938483110322075</v>
+        <v>1.011755422019866</v>
       </c>
       <c r="G5">
-        <v>-4.852549143948951</v>
+        <v>-4.700376607690812</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.34126908913128</v>
       </c>
       <c r="E6">
-        <v>-12.15265567995784</v>
+        <v>-13.38527913400167</v>
       </c>
       <c r="F6">
-        <v>2.364371721396135</v>
+        <v>0.6341397509543147</v>
       </c>
       <c r="G6">
-        <v>-5.421178377410787</v>
+        <v>-4.51786954265633</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.04011703184678</v>
       </c>
       <c r="E7">
-        <v>-10.67638673887933</v>
+        <v>-15.88640061317808</v>
       </c>
       <c r="F7">
-        <v>2.059419645142777</v>
+        <v>0.3838769992258692</v>
       </c>
       <c r="G7">
-        <v>-4.832844776899209</v>
+        <v>-2.748882844292311</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.639582297459773</v>
       </c>
       <c r="E8">
-        <v>-11.95614707886899</v>
+        <v>-13.948702813088</v>
       </c>
       <c r="F8">
-        <v>2.251086069852921</v>
+        <v>0.7288073557556231</v>
       </c>
       <c r="G8">
-        <v>-6.125980280539467</v>
+        <v>-6.862169465925975</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.147884188682747</v>
       </c>
       <c r="E9">
-        <v>-14.97856384343838</v>
+        <v>-14.11107577710703</v>
       </c>
       <c r="F9">
-        <v>2.113135782382652</v>
+        <v>1.255920114120912</v>
       </c>
       <c r="G9">
-        <v>-4.398868672701688</v>
+        <v>-5.725245364101768</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.571167628176346</v>
       </c>
       <c r="E10">
-        <v>-13.73531206089856</v>
+        <v>-16.80905002139687</v>
       </c>
       <c r="F10">
-        <v>2.638200808999278</v>
+        <v>1.038282496103476</v>
       </c>
       <c r="G10">
-        <v>-4.949620960251461</v>
+        <v>-4.268158403174644</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.92128751403922</v>
       </c>
       <c r="E11">
-        <v>-14.22415630155256</v>
+        <v>-17.53841057354627</v>
       </c>
       <c r="F11">
-        <v>2.45704385674399</v>
+        <v>1.027934561651995</v>
       </c>
       <c r="G11">
-        <v>-3.123947790618501</v>
+        <v>-3.891434873533279</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.216850121152731</v>
       </c>
       <c r="E12">
-        <v>-14.75005704501134</v>
+        <v>-18.64640136595099</v>
       </c>
       <c r="F12">
-        <v>2.112464291074506</v>
+        <v>1.85491253287025</v>
       </c>
       <c r="G12">
-        <v>-2.939792073905462</v>
+        <v>-4.745962819766576</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.477318908694333</v>
       </c>
       <c r="E13">
-        <v>-15.7370424834571</v>
+        <v>-19.87494919338791</v>
       </c>
       <c r="F13">
-        <v>2.374825764143951</v>
+        <v>1.436168019180737</v>
       </c>
       <c r="G13">
-        <v>-3.120912020358989</v>
+        <v>-4.716359921554413</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.738859566470817</v>
       </c>
       <c r="E14">
-        <v>-16.3669849172421</v>
+        <v>-19.61888210215018</v>
       </c>
       <c r="F14">
-        <v>2.402667314137377</v>
+        <v>1.561480333445799</v>
       </c>
       <c r="G14">
-        <v>-1.619324706292982</v>
+        <v>-3.473448704290438</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.031312852625639</v>
       </c>
       <c r="E15">
-        <v>-17.6639489299869</v>
+        <v>-21.18612808604279</v>
       </c>
       <c r="F15">
-        <v>2.77232644668376</v>
+        <v>2.0091908283287</v>
       </c>
       <c r="G15">
-        <v>-1.483549302090852</v>
+        <v>-1.625790201731178</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.381857859779617</v>
       </c>
       <c r="E16">
-        <v>-19.70481895339374</v>
+        <v>-20.92962173282632</v>
       </c>
       <c r="F16">
-        <v>2.881353513020358</v>
+        <v>1.97403730812369</v>
       </c>
       <c r="G16">
-        <v>-0.7354553949451245</v>
+        <v>-1.872829730962673</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.813033532302868</v>
       </c>
       <c r="E17">
-        <v>-19.83018522782209</v>
+        <v>-22.45880136421045</v>
       </c>
       <c r="F17">
-        <v>3.127388561807538</v>
+        <v>1.877358396809774</v>
       </c>
       <c r="G17">
-        <v>0.739412506073425</v>
+        <v>-2.631855059479074</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.336234722846227</v>
       </c>
       <c r="E18">
-        <v>-19.10384969630982</v>
+        <v>-22.53595297587914</v>
       </c>
       <c r="F18">
-        <v>3.651272143811245</v>
+        <v>2.254757100164909</v>
       </c>
       <c r="G18">
-        <v>1.180334134812337</v>
+        <v>-1.472104746161592</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.967976385716412</v>
       </c>
       <c r="E19">
-        <v>-21.03386720448289</v>
+        <v>-22.95379527256688</v>
       </c>
       <c r="F19">
-        <v>3.41392372197025</v>
+        <v>2.321290169378436</v>
       </c>
       <c r="G19">
-        <v>1.217372518305703</v>
+        <v>-1.225469103485888</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.71241062084861</v>
       </c>
       <c r="E20">
-        <v>-22.4345649713214</v>
+        <v>-23.5440773309927</v>
       </c>
       <c r="F20">
-        <v>3.526756433621649</v>
+        <v>2.931754953779218</v>
       </c>
       <c r="G20">
-        <v>2.449882001485287</v>
+        <v>0.7903651124683478</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.567176075154865</v>
       </c>
       <c r="E21">
-        <v>-22.51181168094424</v>
+        <v>-23.69413284571087</v>
       </c>
       <c r="F21">
-        <v>3.743532515621085</v>
+        <v>2.648045124969649</v>
       </c>
       <c r="G21">
-        <v>3.351134987459857</v>
+        <v>1.257668478609711</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.524874551670978</v>
       </c>
       <c r="E22">
-        <v>-23.92787456009078</v>
+        <v>-24.95101080653978</v>
       </c>
       <c r="F22">
-        <v>3.404953611665201</v>
+        <v>2.869616668481036</v>
       </c>
       <c r="G22">
-        <v>3.27753493903078</v>
+        <v>0.1241542386909534</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.569962494599587</v>
       </c>
       <c r="E23">
-        <v>-23.12022574929678</v>
+        <v>-25.87759998714524</v>
       </c>
       <c r="F23">
-        <v>4.129860152927469</v>
+        <v>3.14727198957588</v>
       </c>
       <c r="G23">
-        <v>3.244280509088801</v>
+        <v>0.8732611727716983</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.69259917566833</v>
       </c>
       <c r="E24">
-        <v>-24.19683874530235</v>
+        <v>-28.13766173794534</v>
       </c>
       <c r="F24">
-        <v>4.071497422531694</v>
+        <v>3.210691492959652</v>
       </c>
       <c r="G24">
-        <v>3.101360947612925</v>
+        <v>1.780479761808035</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.877294812846666</v>
       </c>
       <c r="E25">
-        <v>-24.67658075320094</v>
+        <v>-28.44071627548666</v>
       </c>
       <c r="F25">
-        <v>3.66183387856131</v>
+        <v>3.149467005974679</v>
       </c>
       <c r="G25">
-        <v>2.682706048171151</v>
+        <v>0.4522458543604244</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.106315615712315</v>
       </c>
       <c r="E26">
-        <v>-25.91111522327601</v>
+        <v>-28.21754854791466</v>
       </c>
       <c r="F26">
-        <v>3.900986141439991</v>
+        <v>2.862792479691407</v>
       </c>
       <c r="G26">
-        <v>3.373249431662189</v>
+        <v>0.5172848320249461</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.361442195782185</v>
       </c>
       <c r="E27">
-        <v>-26.15955636428482</v>
+        <v>-24.87577473937634</v>
       </c>
       <c r="F27">
-        <v>4.196040055721852</v>
+        <v>3.674812348538337</v>
       </c>
       <c r="G27">
-        <v>3.943259162613902</v>
+        <v>1.562321431861142</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.621818939825078</v>
       </c>
       <c r="E28">
-        <v>-26.19568452991801</v>
+        <v>-27.65183346098044</v>
       </c>
       <c r="F28">
-        <v>3.950671747125072</v>
+        <v>3.427307620661629</v>
       </c>
       <c r="G28">
-        <v>3.681537363915739</v>
+        <v>1.767727540390763</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.873755878003203</v>
       </c>
       <c r="E29">
-        <v>-26.01004879492158</v>
+        <v>-26.2969910219436</v>
       </c>
       <c r="F29">
-        <v>4.22399563254119</v>
+        <v>2.32799082910666</v>
       </c>
       <c r="G29">
-        <v>3.233666900089898</v>
+        <v>1.360609892153349</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.105814333785376</v>
       </c>
       <c r="E30">
-        <v>-25.19064859407768</v>
+        <v>-27.45964502409491</v>
       </c>
       <c r="F30">
-        <v>3.628081938091465</v>
+        <v>3.302719059999923</v>
       </c>
       <c r="G30">
-        <v>2.425582597227037</v>
+        <v>1.796211474210652</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.309067172444541</v>
       </c>
       <c r="E31">
-        <v>-25.16984478448644</v>
+        <v>-27.29599955887973</v>
       </c>
       <c r="F31">
-        <v>4.16166888623907</v>
+        <v>2.805901012091076</v>
       </c>
       <c r="G31">
-        <v>2.933701679322075</v>
+        <v>1.203557611770324</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.477823047279998</v>
       </c>
       <c r="E32">
-        <v>-24.71118282309356</v>
+        <v>-24.96325580025652</v>
       </c>
       <c r="F32">
-        <v>3.495665119089742</v>
+        <v>3.502380032171205</v>
       </c>
       <c r="G32">
-        <v>1.751744226527161</v>
+        <v>1.289300741237448</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.606710026802442</v>
       </c>
       <c r="E33">
-        <v>-25.41451823512087</v>
+        <v>-25.51297631699564</v>
       </c>
       <c r="F33">
-        <v>3.913829996414205</v>
+        <v>3.083139818530159</v>
       </c>
       <c r="G33">
-        <v>2.607205746602532</v>
+        <v>-0.1909070697359462</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.696497084530878</v>
       </c>
       <c r="E34">
-        <v>-25.3454046648158</v>
+        <v>-25.80331489952341</v>
       </c>
       <c r="F34">
-        <v>4.503518142910337</v>
+        <v>3.552274687037125</v>
       </c>
       <c r="G34">
-        <v>2.842804030450305</v>
+        <v>0.264829250291204</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.750398314506332</v>
       </c>
       <c r="E35">
-        <v>-24.04754854269149</v>
+        <v>-27.35801701041478</v>
       </c>
       <c r="F35">
-        <v>4.447022601788865</v>
+        <v>3.134257094362798</v>
       </c>
       <c r="G35">
-        <v>1.825572702598448</v>
+        <v>-0.4041657922847175</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.772368847878677</v>
       </c>
       <c r="E36">
-        <v>-23.68143500459336</v>
+        <v>-25.28001350014504</v>
       </c>
       <c r="F36">
-        <v>4.207984365736097</v>
+        <v>3.220825627112549</v>
       </c>
       <c r="G36">
-        <v>1.638523569084087</v>
+        <v>-0.2785007941595225</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.768029345757346</v>
       </c>
       <c r="E37">
-        <v>-21.89785928888033</v>
+        <v>-23.87344683099259</v>
       </c>
       <c r="F37">
-        <v>4.476270482635201</v>
+        <v>3.219846896856808</v>
       </c>
       <c r="G37">
-        <v>2.574024148662417</v>
+        <v>0.002557901033522714</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.74165539868561</v>
       </c>
       <c r="E38">
-        <v>-22.17699442671313</v>
+        <v>-26.71208000643469</v>
       </c>
       <c r="F38">
-        <v>4.456634112989667</v>
+        <v>3.613267952958445</v>
       </c>
       <c r="G38">
-        <v>1.784992035378062</v>
+        <v>0.4100330881891775</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.702012308037342</v>
       </c>
       <c r="E39">
-        <v>-21.23352309500707</v>
+        <v>-21.29238420015877</v>
       </c>
       <c r="F39">
-        <v>4.677945928730922</v>
+        <v>4.026084655406468</v>
       </c>
       <c r="G39">
-        <v>1.257453293149659</v>
+        <v>-0.4900744490288048</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.659191794436734</v>
       </c>
       <c r="E40">
-        <v>-20.17571232308135</v>
+        <v>-23.53902355400014</v>
       </c>
       <c r="F40">
-        <v>4.860222561068425</v>
+        <v>3.713133280574225</v>
       </c>
       <c r="G40">
-        <v>0.6476210099060528</v>
+        <v>-1.518770196083159</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.621494708979903</v>
       </c>
       <c r="E41">
-        <v>-20.04465828529937</v>
+        <v>-20.68237158048153</v>
       </c>
       <c r="F41">
-        <v>4.851273038940277</v>
+        <v>3.8821542943995</v>
       </c>
       <c r="G41">
-        <v>0.8158794869395108</v>
+        <v>-2.456862932818738</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.596435547280715</v>
       </c>
       <c r="E42">
-        <v>-20.52354894008451</v>
+        <v>-20.35393041765321</v>
       </c>
       <c r="F42">
-        <v>4.962249647258781</v>
+        <v>4.266234653011875</v>
       </c>
       <c r="G42">
-        <v>1.335148486410814</v>
+        <v>-0.06017693693566628</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.587138271022336</v>
       </c>
       <c r="E43">
-        <v>-18.32994707382098</v>
+        <v>-20.79776162667098</v>
       </c>
       <c r="F43">
-        <v>5.346801950233957</v>
+        <v>4.301297901979704</v>
       </c>
       <c r="G43">
-        <v>0.1467917490884898</v>
+        <v>-1.510669291148562</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.598483662503737</v>
       </c>
       <c r="E44">
-        <v>-16.86143993719161</v>
+        <v>-20.86812052732815</v>
       </c>
       <c r="F44">
-        <v>5.244188892854888</v>
+        <v>4.610595667265028</v>
       </c>
       <c r="G44">
-        <v>0.654960489366617</v>
+        <v>-2.451622339230072</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.634683794480229</v>
       </c>
       <c r="E45">
-        <v>-16.24712979568109</v>
+        <v>-17.78824648454944</v>
       </c>
       <c r="F45">
-        <v>5.717587097686217</v>
+        <v>3.948023790834458</v>
       </c>
       <c r="G45">
-        <v>0.3734681127079272</v>
+        <v>-1.193509096849764</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.695134005269232</v>
       </c>
       <c r="E46">
-        <v>-15.5027754660923</v>
+        <v>-17.82916577568275</v>
       </c>
       <c r="F46">
-        <v>5.924544203009929</v>
+        <v>5.13074803813196</v>
       </c>
       <c r="G46">
-        <v>-0.9136124031410034</v>
+        <v>-1.930227969522557</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.776373805373193</v>
       </c>
       <c r="E47">
-        <v>-15.25582872150602</v>
+        <v>-19.25928050967509</v>
       </c>
       <c r="F47">
-        <v>5.567434356137487</v>
+        <v>3.89833343403163</v>
       </c>
       <c r="G47">
-        <v>-0.2494077199604073</v>
+        <v>-2.880870984397514</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.870055755017753</v>
       </c>
       <c r="E48">
-        <v>-13.90054702049043</v>
+        <v>-15.72513712529093</v>
       </c>
       <c r="F48">
-        <v>5.913402831894812</v>
+        <v>4.30744584834344</v>
       </c>
       <c r="G48">
-        <v>-1.023214634309655</v>
+        <v>-3.362790409094759</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.969894714418707</v>
       </c>
       <c r="E49">
-        <v>-13.70843103918902</v>
+        <v>-16.32939405450443</v>
       </c>
       <c r="F49">
-        <v>5.401951341327305</v>
+        <v>4.530097479289156</v>
       </c>
       <c r="G49">
-        <v>-0.4095719131503474</v>
+        <v>-2.807227898876426</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.071514672166377</v>
       </c>
       <c r="E50">
-        <v>-12.92754550978036</v>
+        <v>-14.22950442935562</v>
       </c>
       <c r="F50">
-        <v>5.822989061182374</v>
+        <v>4.528795673026665</v>
       </c>
       <c r="G50">
-        <v>-0.7217464258670024</v>
+        <v>-1.51644950366013</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.168687041002342</v>
       </c>
       <c r="E51">
-        <v>-12.5318927357302</v>
+        <v>-15.69940180750534</v>
       </c>
       <c r="F51">
-        <v>5.229986218205227</v>
+        <v>4.611001095979381</v>
       </c>
       <c r="G51">
-        <v>-0.4574953703768371</v>
+        <v>-3.044335791490107</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.25612369717614</v>
       </c>
       <c r="E52">
-        <v>-11.3703074534447</v>
+        <v>-13.67117075505391</v>
       </c>
       <c r="F52">
-        <v>6.043608797438582</v>
+        <v>5.17646170938112</v>
       </c>
       <c r="G52">
-        <v>-1.194810141246698</v>
+        <v>-2.021655305680609</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.327318545090546</v>
       </c>
       <c r="E53">
-        <v>-11.25792884247035</v>
+        <v>-12.43142401139602</v>
       </c>
       <c r="F53">
-        <v>6.041068533150217</v>
+        <v>5.378165662183319</v>
       </c>
       <c r="G53">
-        <v>-1.004811311656846</v>
+        <v>-1.099840521361626</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.379748027808742</v>
       </c>
       <c r="E54">
-        <v>-10.40699234863703</v>
+        <v>-11.43901346108907</v>
       </c>
       <c r="F54">
-        <v>6.027435992630114</v>
+        <v>5.463243927666642</v>
       </c>
       <c r="G54">
-        <v>-0.9805714972183024</v>
+        <v>-2.675355627865097</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.414540344818797</v>
       </c>
       <c r="E55">
-        <v>-9.0383425923508</v>
+        <v>-14.36063545119573</v>
       </c>
       <c r="F55">
-        <v>6.082908459730212</v>
+        <v>5.050924508876066</v>
       </c>
       <c r="G55">
-        <v>-1.974089387372361</v>
+        <v>-2.139020766138851</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.431026594785309</v>
       </c>
       <c r="E56">
-        <v>-7.895192727750525</v>
+        <v>-11.77560134865718</v>
       </c>
       <c r="F56">
-        <v>6.158935845906798</v>
+        <v>5.197914589711663</v>
       </c>
       <c r="G56">
-        <v>-1.084900029342895</v>
+        <v>-1.816649773161241</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.428927701429058</v>
       </c>
       <c r="E57">
-        <v>-7.82852906188361</v>
+        <v>-11.47443518477707</v>
       </c>
       <c r="F57">
-        <v>5.61104961704869</v>
+        <v>4.804309823723836</v>
       </c>
       <c r="G57">
-        <v>-1.374976650584915</v>
+        <v>-2.72907916087639</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.406369424852878</v>
       </c>
       <c r="E58">
-        <v>-5.82004668457963</v>
+        <v>-9.988665505230463</v>
       </c>
       <c r="F58">
-        <v>5.557780084876969</v>
+        <v>5.177706502230656</v>
       </c>
       <c r="G58">
-        <v>-1.585381682878834</v>
+        <v>-2.984610239416115</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.363947029608753</v>
       </c>
       <c r="E59">
-        <v>-7.209694974839425</v>
+        <v>-10.39653610215332</v>
       </c>
       <c r="F59">
-        <v>5.707468800592475</v>
+        <v>5.122018651126059</v>
       </c>
       <c r="G59">
-        <v>-2.740407847711777</v>
+        <v>-2.831970916236939</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.305427712384684</v>
       </c>
       <c r="E60">
-        <v>-7.633356360627025</v>
+        <v>-11.87753729856984</v>
       </c>
       <c r="F60">
-        <v>5.346447200108898</v>
+        <v>4.743815425165879</v>
       </c>
       <c r="G60">
-        <v>-1.368759446062163</v>
+        <v>-2.997130722645639</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.231911127308639</v>
       </c>
       <c r="E61">
-        <v>-6.704856163990326</v>
+        <v>-10.42113024448897</v>
       </c>
       <c r="F61">
-        <v>5.675025001208782</v>
+        <v>4.780001521627756</v>
       </c>
       <c r="G61">
-        <v>-2.361704611837927</v>
+        <v>-4.599292410194705</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.144073622890933</v>
       </c>
       <c r="E62">
-        <v>-7.380563356096842</v>
+        <v>-8.599035328866698</v>
       </c>
       <c r="F62">
-        <v>5.725090696313569</v>
+        <v>4.858803560568191</v>
       </c>
       <c r="G62">
-        <v>-2.237555843569719</v>
+        <v>-3.273640728267726</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.040898951142031</v>
       </c>
       <c r="E63">
-        <v>-5.554596595198008</v>
+        <v>-8.551585978214328</v>
       </c>
       <c r="F63">
-        <v>5.4215940457965</v>
+        <v>4.353195944828655</v>
       </c>
       <c r="G63">
-        <v>-1.671376413806942</v>
+        <v>-4.820155455847182</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.923406204563121</v>
       </c>
       <c r="E64">
-        <v>-4.833011432919784</v>
+        <v>-5.962766071405369</v>
       </c>
       <c r="F64">
-        <v>4.799677483921175</v>
+        <v>4.284092520914371</v>
       </c>
       <c r="G64">
-        <v>-2.186762143360681</v>
+        <v>-2.566577722535725</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.796128418258937</v>
       </c>
       <c r="E65">
-        <v>-3.845709001293484</v>
+        <v>-7.691003834744668</v>
       </c>
       <c r="F65">
-        <v>5.012337514246384</v>
+        <v>4.356532813192486</v>
       </c>
       <c r="G65">
-        <v>-1.849258646723062</v>
+        <v>-3.595829641240676</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.66083734141304</v>
       </c>
       <c r="E66">
-        <v>-4.226390640274285</v>
+        <v>-7.417746656173824</v>
       </c>
       <c r="F66">
-        <v>4.698530938219804</v>
+        <v>3.654466478642686</v>
       </c>
       <c r="G66">
-        <v>-1.409028922001858</v>
+        <v>-4.116757224027155</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.519290646761418</v>
       </c>
       <c r="E67">
-        <v>-3.851822441203839</v>
+        <v>-6.421278593156</v>
       </c>
       <c r="F67">
-        <v>4.692058332143403</v>
+        <v>3.62047539857961</v>
       </c>
       <c r="G67">
-        <v>-2.157533336794455</v>
+        <v>-3.975721362963124</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.3717274567093</v>
       </c>
       <c r="E68">
-        <v>-2.822196891501853</v>
+        <v>-7.235448406521046</v>
       </c>
       <c r="F68">
-        <v>4.110540524465023</v>
+        <v>2.784703108412919</v>
       </c>
       <c r="G68">
-        <v>-2.314148625166297</v>
+        <v>-3.631176335963475</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.219666387374194</v>
       </c>
       <c r="E69">
-        <v>-4.324128694781835</v>
+        <v>-6.132597432115031</v>
       </c>
       <c r="F69">
-        <v>4.55872454741664</v>
+        <v>2.57481773085156</v>
       </c>
       <c r="G69">
-        <v>-2.028551172038911</v>
+        <v>-3.504677080362383</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.068009632137713</v>
       </c>
       <c r="E70">
-        <v>-3.474156765912147</v>
+        <v>-4.308519044877395</v>
       </c>
       <c r="F70">
-        <v>4.090646010755273</v>
+        <v>3.22587448157097</v>
       </c>
       <c r="G70">
-        <v>-1.82832606727825</v>
+        <v>-2.476855317330397</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.919055386432851</v>
       </c>
       <c r="E71">
-        <v>-3.581327631777674</v>
+        <v>-6.952599920001956</v>
       </c>
       <c r="F71">
-        <v>3.363596715389416</v>
+        <v>3.175756524170974</v>
       </c>
       <c r="G71">
-        <v>-2.848368048292949</v>
+        <v>-3.969702791172729</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.77530189260204</v>
       </c>
       <c r="E72">
-        <v>-3.75157561209604</v>
+        <v>-6.409509089210065</v>
       </c>
       <c r="F72">
-        <v>3.498957643687941</v>
+        <v>2.905316567226872</v>
       </c>
       <c r="G72">
-        <v>-1.534074848111209</v>
+        <v>-5.62094000579595</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.638343502657891</v>
       </c>
       <c r="E73">
-        <v>-2.642787808265969</v>
+        <v>-5.849391196149334</v>
       </c>
       <c r="F73">
-        <v>2.941508998512409</v>
+        <v>2.601924441300222</v>
       </c>
       <c r="G73">
-        <v>-1.017613191257208</v>
+        <v>-2.967229875334942</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.510582713315964</v>
       </c>
       <c r="E74">
-        <v>-4.401248607132461</v>
+        <v>-8.186758526734382</v>
       </c>
       <c r="F74">
-        <v>3.563289361679006</v>
+        <v>2.720664376016209</v>
       </c>
       <c r="G74">
-        <v>-1.190082682216619</v>
+        <v>-2.440253925848215</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.398871169819561</v>
       </c>
       <c r="E75">
-        <v>-3.61027816610871</v>
+        <v>-7.953813823779818</v>
       </c>
       <c r="F75">
-        <v>3.225377197913522</v>
+        <v>2.116941427697453</v>
       </c>
       <c r="G75">
-        <v>-1.254284091859705</v>
+        <v>-2.356308422608915</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.30728221740633</v>
       </c>
       <c r="E76">
-        <v>-3.815168972585755</v>
+        <v>-5.851347496920647</v>
       </c>
       <c r="F76">
-        <v>2.913412471866598</v>
+        <v>2.176523611648116</v>
       </c>
       <c r="G76">
-        <v>-0.1866099816259722</v>
+        <v>-4.083674942453218</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.239858043187473</v>
       </c>
       <c r="E77">
-        <v>-5.114705158566918</v>
+        <v>-7.462048717390863</v>
       </c>
       <c r="F77">
-        <v>2.827819501960758</v>
+        <v>2.645487439916214</v>
       </c>
       <c r="G77">
-        <v>-0.3799789465748022</v>
+        <v>-1.623575446765406</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.199418780432965</v>
       </c>
       <c r="E78">
-        <v>-5.507477823148198</v>
+        <v>-10.21862141533996</v>
       </c>
       <c r="F78">
-        <v>2.8568219083902</v>
+        <v>1.490609493729883</v>
       </c>
       <c r="G78">
-        <v>0.05918147193721709</v>
+        <v>-1.623615173311877</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.187203142282894</v>
       </c>
       <c r="E79">
-        <v>-4.206687249866912</v>
+        <v>-8.832967239154934</v>
       </c>
       <c r="F79">
-        <v>2.610875547134285</v>
+        <v>2.50128151407996</v>
       </c>
       <c r="G79">
-        <v>0.3527507187231682</v>
+        <v>-0.6836122518001377</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.210149390967601</v>
       </c>
       <c r="E80">
-        <v>-5.83493630711685</v>
+        <v>-9.677332917203126</v>
       </c>
       <c r="F80">
-        <v>3.250083010194378</v>
+        <v>1.191905137312934</v>
       </c>
       <c r="G80">
-        <v>0.9012087982142257</v>
+        <v>-2.268522686544062</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.271790368675732</v>
       </c>
       <c r="E81">
-        <v>-7.376247720367533</v>
+        <v>-10.51748258595018</v>
       </c>
       <c r="F81">
-        <v>2.154388154068019</v>
+        <v>1.787993039413357</v>
       </c>
       <c r="G81">
-        <v>0.7218798568974448</v>
+        <v>-0.1913539933837478</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.375612502488375</v>
       </c>
       <c r="E82">
-        <v>-7.685565137461457</v>
+        <v>-9.462080962196531</v>
       </c>
       <c r="F82">
-        <v>2.554047427770572</v>
+        <v>1.870105023717061</v>
       </c>
       <c r="G82">
-        <v>1.599796807365692</v>
+        <v>-0.2537312924346955</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.524174050115322</v>
       </c>
       <c r="E83">
-        <v>-8.398704695715377</v>
+        <v>-10.36562473857696</v>
       </c>
       <c r="F83">
-        <v>2.18439463004785</v>
+        <v>1.614334934667675</v>
       </c>
       <c r="G83">
-        <v>2.094190367654912</v>
+        <v>-0.0669536236545544</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.716397454849375</v>
       </c>
       <c r="E84">
-        <v>-9.963853996142436</v>
+        <v>-10.75320324347144</v>
       </c>
       <c r="F84">
-        <v>2.735761844508094</v>
+        <v>1.043271169737111</v>
       </c>
       <c r="G84">
-        <v>2.552134821556756</v>
+        <v>0.8469357146434139</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.959910692753922</v>
       </c>
       <c r="E85">
-        <v>-11.30175994239059</v>
+        <v>-13.46804605343986</v>
       </c>
       <c r="F85">
-        <v>2.51052560550838</v>
+        <v>1.690705985027911</v>
       </c>
       <c r="G85">
-        <v>2.611671672535009</v>
+        <v>-1.14002061257176</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.257928272016238</v>
       </c>
       <c r="E86">
-        <v>-11.58991580044667</v>
+        <v>-15.99041060418626</v>
       </c>
       <c r="F86">
-        <v>2.062864205508858</v>
+        <v>0.8679802641926109</v>
       </c>
       <c r="G86">
-        <v>2.925815959847531</v>
+        <v>0.4732181603517074</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.612787723252525</v>
       </c>
       <c r="E87">
-        <v>-11.14223086004838</v>
+        <v>-16.79101310942432</v>
       </c>
       <c r="F87">
-        <v>1.606538350445966</v>
+        <v>1.213345347996153</v>
       </c>
       <c r="G87">
-        <v>2.138505330243596</v>
+        <v>2.212486091409689</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.024489081892211</v>
       </c>
       <c r="E88">
-        <v>-13.82172440191292</v>
+        <v>-18.4514007467067</v>
       </c>
       <c r="F88">
-        <v>2.383797458154915</v>
+        <v>0.9098677019500688</v>
       </c>
       <c r="G88">
-        <v>2.912832000242509</v>
+        <v>1.843737665972429</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.484758011788713</v>
       </c>
       <c r="E89">
-        <v>-15.74431974118743</v>
+        <v>-20.5223036097324</v>
       </c>
       <c r="F89">
-        <v>1.5266562240712</v>
+        <v>1.087450229954209</v>
       </c>
       <c r="G89">
-        <v>2.924713548182953</v>
+        <v>2.236388230203227</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.995275180277416</v>
       </c>
       <c r="E90">
-        <v>-18.07120365444472</v>
+        <v>-18.84222163899067</v>
       </c>
       <c r="F90">
-        <v>1.676251501137695</v>
+        <v>0.3459021069325044</v>
       </c>
       <c r="G90">
-        <v>2.965989429966586</v>
+        <v>2.204818867940737</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.550144949422604</v>
       </c>
       <c r="E91">
-        <v>-17.77288137224141</v>
+        <v>-23.84910175472735</v>
       </c>
       <c r="F91">
-        <v>1.526684730777679</v>
+        <v>0.3560338655265283</v>
       </c>
       <c r="G91">
-        <v>2.473813935188678</v>
+        <v>0.6466311567898106</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.140807721541599</v>
       </c>
       <c r="E92">
-        <v>-19.27856728047376</v>
+        <v>-23.39102849495547</v>
       </c>
       <c r="F92">
-        <v>1.694708009876227</v>
+        <v>-0.4789449879765271</v>
       </c>
       <c r="G92">
-        <v>2.719893406213784</v>
+        <v>1.662654135519834</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.755281609420942</v>
       </c>
       <c r="E93">
-        <v>-21.48371222698285</v>
+        <v>-24.76941447035819</v>
       </c>
       <c r="F93">
-        <v>0.8954860685319632</v>
+        <v>0.3549902033282537</v>
       </c>
       <c r="G93">
-        <v>2.465964631715067</v>
+        <v>2.466818752464198</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.371159767699888</v>
       </c>
       <c r="E94">
-        <v>-23.35612754577835</v>
+        <v>-26.22387880908977</v>
       </c>
       <c r="F94">
-        <v>1.006999553155801</v>
+        <v>0.1956765149116647</v>
       </c>
       <c r="G94">
-        <v>2.21116518373952</v>
+        <v>1.915569883083535</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.979056316471343</v>
       </c>
       <c r="E95">
-        <v>-24.64106846003279</v>
+        <v>-26.34801786706203</v>
       </c>
       <c r="F95">
-        <v>0.6127296306834888</v>
+        <v>-0.1465805460328274</v>
       </c>
       <c r="G95">
-        <v>2.368366438671813</v>
+        <v>0.1447756268550736</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.563466983965947</v>
       </c>
       <c r="E96">
-        <v>-29.18069609918404</v>
+        <v>-32.1520226199989</v>
       </c>
       <c r="F96">
-        <v>0.7620002480373185</v>
+        <v>0.4274225770767922</v>
       </c>
       <c r="G96">
-        <v>2.795781041610498</v>
+        <v>0.5835056744469878</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.10815202679921</v>
       </c>
       <c r="E97">
-        <v>-30.60092064594363</v>
+        <v>-31.12122872400293</v>
       </c>
       <c r="F97">
-        <v>0.3896923673473628</v>
+        <v>-0.199481866579209</v>
       </c>
       <c r="G97">
-        <v>2.709448635037384</v>
+        <v>-1.768266150104792</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.59974797338684</v>
       </c>
       <c r="E98">
-        <v>-33.26182480200669</v>
+        <v>-36.88215183946782</v>
       </c>
       <c r="F98">
-        <v>0.0653335588062096</v>
+        <v>-0.7063414018449001</v>
       </c>
       <c r="G98">
-        <v>2.4020346868062</v>
+        <v>0.6455552294895476</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.01569873510731</v>
       </c>
       <c r="E99">
-        <v>-35.29594287066809</v>
+        <v>-35.68822419581954</v>
       </c>
       <c r="F99">
-        <v>-0.4387584503722511</v>
+        <v>-1.44846441011391</v>
       </c>
       <c r="G99">
-        <v>1.579013202470148</v>
+        <v>-0.9565501787853506</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.35695025281658</v>
       </c>
       <c r="E100">
-        <v>-37.17937143825025</v>
+        <v>-39.59056874481935</v>
       </c>
       <c r="F100">
-        <v>0.04114324280082975</v>
+        <v>-1.34471979485826</v>
       </c>
       <c r="G100">
-        <v>2.563258254568707</v>
+        <v>-0.7760493043476677</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.61369034301384</v>
       </c>
       <c r="E101">
-        <v>-39.08240829828563</v>
+        <v>-40.67929314455844</v>
       </c>
       <c r="F101">
-        <v>-0.2866902165187976</v>
+        <v>-1.519302783858558</v>
       </c>
       <c r="G101">
-        <v>0.9814928380870913</v>
+        <v>-0.9189556236413871</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.79247499420653</v>
       </c>
       <c r="E102">
-        <v>-41.50493131834791</v>
+        <v>-41.24087826319766</v>
       </c>
       <c r="F102">
-        <v>-0.4206923251418756</v>
+        <v>-1.619433382215175</v>
       </c>
       <c r="G102">
-        <v>1.019696533610281</v>
+        <v>-1.883668457058247</v>
       </c>
     </row>
   </sheetData>
